--- a/artfynd/A 1547-2022 artfynd.xlsx
+++ b/artfynd/A 1547-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1547-2022 artfynd.xlsx
+++ b/artfynd/A 1547-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>431879</v>
+        <v>416886</v>
       </c>
       <c r="B2" t="n">
-        <v>99120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,21 +704,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Häverö Hummelmyren, V-ut, Upl</t>
+          <t>ARKIV// Hummelmyren, V-ut (*hällebräcka* /plant/), Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>705957.1089071045</v>
+        <v>705957</v>
       </c>
       <c r="R2" t="n">
-        <v>6668108.534711158</v>
+        <v>6668109</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,33 +738,23 @@
           <t>Häverö</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Arkiv-AB-Nor-0412</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2006-06-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1994-06-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2006-06-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>avverkning. Funnen 1994-06-24 av Ebbe Zachrisson</t>
+          <t>1994-06-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
@@ -790,15 +770,130 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>AB-län Floraväktarna</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
           <t>Ebbe Zachrisson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>431876</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101947</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1449</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Hällebräcka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Saxifraga osloënsis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Häverö Hattängen, 500 m V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>705882</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6668244</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Häverö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2006-06-10</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2006-06-10</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>traktorväg efter skogsavverkning, ett par år gammal</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
         <is>
           <t>Ebbe Zachrisson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ebbe Zachrisson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri AB-län</t>
         </is>

--- a/artfynd/A 1547-2022 artfynd.xlsx
+++ b/artfynd/A 1547-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/416886</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,8 +908,17 @@
           <t>Floraväkteri AB-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/431876</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>